--- a/5_Judgemental_Forecasts_Derivations_Analysis/0_Main/AR2/4_Main_Analysis_Tables/Summary_Statistics_All_Horizons.xlsx
+++ b/5_Judgemental_Forecasts_Derivations_Analysis/0_Main/AR2/4_Main_Analysis_Tables/Summary_Statistics_All_Horizons.xlsx
@@ -480,34 +480,34 @@
         <v>15</v>
       </c>
       <c r="C2">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D2">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E2">
         <v>0.4126</v>
       </c>
       <c r="F2">
-        <v>0.9939</v>
+        <v>1.1357</v>
       </c>
       <c r="G2">
-        <v>0.5814</v>
+        <v>0.7231</v>
       </c>
       <c r="H2">
-        <v>4.3035</v>
+        <v>7.1832</v>
       </c>
       <c r="I2">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="J2">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="K2">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="L2">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="M2">
         <v>52</v>
@@ -524,37 +524,37 @@
         <v>16</v>
       </c>
       <c r="C3">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>0.3691</v>
+        <v>0.404</v>
       </c>
       <c r="F3">
-        <v>0.8344</v>
+        <v>0.8248</v>
       </c>
       <c r="G3">
-        <v>0.4653</v>
+        <v>0.4208</v>
       </c>
       <c r="H3">
-        <v>2.7277</v>
+        <v>2.4811</v>
       </c>
       <c r="I3">
+        <v>26</v>
+      </c>
+      <c r="J3">
+        <v>9</v>
+      </c>
+      <c r="K3">
+        <v>23</v>
+      </c>
+      <c r="L3">
+        <v>12</v>
+      </c>
+      <c r="M3">
         <v>35</v>
-      </c>
-      <c r="J3">
-        <v>6</v>
-      </c>
-      <c r="K3">
-        <v>32</v>
-      </c>
-      <c r="L3">
-        <v>9</v>
-      </c>
-      <c r="M3">
-        <v>41</v>
       </c>
       <c r="N3">
         <v>0</v>
@@ -571,34 +571,34 @@
         <v>0</v>
       </c>
       <c r="D4">
+        <v>17</v>
+      </c>
+      <c r="E4">
+        <v>0.4302</v>
+      </c>
+      <c r="F4">
+        <v>1.7757</v>
+      </c>
+      <c r="G4">
+        <v>1.3455</v>
+      </c>
+      <c r="H4">
+        <v>16.8639</v>
+      </c>
+      <c r="I4">
+        <v>5</v>
+      </c>
+      <c r="J4">
+        <v>12</v>
+      </c>
+      <c r="K4">
         <v>11</v>
       </c>
-      <c r="E4">
-        <v>0.5746</v>
-      </c>
-      <c r="F4">
-        <v>1.5885</v>
-      </c>
-      <c r="G4">
-        <v>1.0139</v>
-      </c>
-      <c r="H4">
-        <v>10.1768</v>
-      </c>
-      <c r="I4">
-        <v>3</v>
-      </c>
-      <c r="J4">
-        <v>8</v>
-      </c>
-      <c r="K4">
-        <v>8</v>
-      </c>
       <c r="L4">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M4">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="N4">
         <v>0</v>
@@ -612,34 +612,34 @@
         <v>15</v>
       </c>
       <c r="C5">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D5">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E5">
         <v>0.6888</v>
       </c>
       <c r="F5">
-        <v>0.9828</v>
+        <v>1.1231</v>
       </c>
       <c r="G5">
-        <v>0.2941</v>
+        <v>0.4344</v>
       </c>
       <c r="H5">
-        <v>2.9536</v>
+        <v>4.2064</v>
       </c>
       <c r="I5">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="J5">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="K5">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="L5">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="M5">
         <v>51</v>
@@ -656,37 +656,37 @@
         <v>16</v>
       </c>
       <c r="C6">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
       <c r="E6">
-        <v>0.638</v>
+        <v>0.7134</v>
       </c>
       <c r="F6">
-        <v>0.8977000000000001</v>
+        <v>0.9635</v>
       </c>
       <c r="G6">
-        <v>0.2597</v>
+        <v>0.2502</v>
       </c>
       <c r="H6">
-        <v>2.3659</v>
+        <v>2.8874</v>
       </c>
       <c r="I6">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="J6">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="K6">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="L6">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="M6">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="N6">
         <v>1</v>
@@ -703,34 +703,34 @@
         <v>0</v>
       </c>
       <c r="D7">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E7">
-        <v>0.8372000000000001</v>
+        <v>0.6473</v>
       </c>
       <c r="F7">
-        <v>1.2319</v>
+        <v>1.3919</v>
       </c>
       <c r="G7">
-        <v>0.3947</v>
+        <v>0.7446</v>
       </c>
       <c r="H7">
-        <v>4.6717</v>
+        <v>6.428</v>
       </c>
       <c r="I7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J7">
+        <v>15</v>
+      </c>
+      <c r="K7">
+        <v>11</v>
+      </c>
+      <c r="L7">
         <v>8</v>
       </c>
-      <c r="K7">
-        <v>6</v>
-      </c>
-      <c r="L7">
-        <v>7</v>
-      </c>
       <c r="M7">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="N7">
         <v>1</v>
@@ -744,34 +744,34 @@
         <v>15</v>
       </c>
       <c r="C8">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="D8">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="E8">
         <v>1.0235</v>
       </c>
       <c r="F8">
-        <v>0.9179</v>
+        <v>0.9693000000000001</v>
       </c>
       <c r="G8">
-        <v>-0.1056</v>
+        <v>-0.0541</v>
       </c>
       <c r="H8">
-        <v>-0.017</v>
+        <v>0.3619</v>
       </c>
       <c r="I8">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="J8">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="K8">
+        <v>22</v>
+      </c>
+      <c r="L8">
         <v>28</v>
-      </c>
-      <c r="L8">
-        <v>22</v>
       </c>
       <c r="M8">
         <v>50</v>
@@ -788,37 +788,37 @@
         <v>16</v>
       </c>
       <c r="C9">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="D9">
         <v>0</v>
       </c>
       <c r="E9">
-        <v>0.9666</v>
+        <v>1.0975</v>
       </c>
       <c r="F9">
-        <v>0.7809</v>
+        <v>0.8669</v>
       </c>
       <c r="G9">
-        <v>-0.1857</v>
+        <v>-0.2305</v>
       </c>
       <c r="H9">
-        <v>-0.5841</v>
+        <v>-0.4741</v>
       </c>
       <c r="I9">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="J9">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="K9">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="L9">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="M9">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="N9">
         <v>2</v>
@@ -835,34 +835,34 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="E10">
-        <v>1.3223</v>
+        <v>0.9213</v>
       </c>
       <c r="F10">
-        <v>1.6368</v>
+        <v>1.1107</v>
       </c>
       <c r="G10">
-        <v>0.3145</v>
+        <v>0.1894</v>
       </c>
       <c r="H10">
-        <v>2.9602</v>
+        <v>1.5164</v>
       </c>
       <c r="I10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J10">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="K10">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="L10">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M10">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="N10">
         <v>2</v>
@@ -876,28 +876,28 @@
         <v>15</v>
       </c>
       <c r="C11">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="D11">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E11">
         <v>1.076</v>
       </c>
       <c r="F11">
-        <v>0.9518</v>
+        <v>1.0322</v>
       </c>
       <c r="G11">
-        <v>-0.1242</v>
+        <v>-0.0437</v>
       </c>
       <c r="H11">
-        <v>-0.3198</v>
+        <v>0.3341</v>
       </c>
       <c r="I11">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="J11">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="K11">
         <v>18</v>
@@ -920,37 +920,37 @@
         <v>16</v>
       </c>
       <c r="C12">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="D12">
         <v>0</v>
       </c>
       <c r="E12">
-        <v>1.0466</v>
+        <v>1.1733</v>
       </c>
       <c r="F12">
-        <v>0.9055</v>
+        <v>0.9459</v>
       </c>
       <c r="G12">
-        <v>-0.1411</v>
+        <v>-0.2273</v>
       </c>
       <c r="H12">
-        <v>-0.3703</v>
+        <v>-0.654</v>
       </c>
       <c r="I12">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="J12">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K12">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="L12">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M12">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="N12">
         <v>3</v>
@@ -967,34 +967,34 @@
         <v>0</v>
       </c>
       <c r="D13">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E13">
-        <v>1.1665</v>
+        <v>0.9223</v>
       </c>
       <c r="F13">
-        <v>1.0946</v>
+        <v>1.1685</v>
       </c>
       <c r="G13">
-        <v>-0.07190000000000001</v>
+        <v>0.2462</v>
       </c>
       <c r="H13">
-        <v>-0.1638</v>
+        <v>1.8943</v>
       </c>
       <c r="I13">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J13">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="K13">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="L13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M13">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="N13">
         <v>3</v>
@@ -1008,34 +1008,34 @@
         <v>15</v>
       </c>
       <c r="C14">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="D14">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="E14">
         <v>0.9593</v>
       </c>
       <c r="F14">
-        <v>0.9401</v>
+        <v>1.0079</v>
       </c>
       <c r="G14">
-        <v>-0.0192</v>
+        <v>0.0486</v>
       </c>
       <c r="H14">
-        <v>-0.0948</v>
+        <v>0.7911</v>
       </c>
       <c r="I14">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="J14">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="K14">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="L14">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="M14">
         <v>48</v>
@@ -1052,37 +1052,37 @@
         <v>16</v>
       </c>
       <c r="C15">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="D15">
         <v>0</v>
       </c>
       <c r="E15">
-        <v>0.831</v>
+        <v>1.1509</v>
       </c>
       <c r="F15">
-        <v>0.802</v>
+        <v>0.9709</v>
       </c>
       <c r="G15">
-        <v>-0.029</v>
+        <v>-0.1801</v>
       </c>
       <c r="H15">
-        <v>-0.0596</v>
+        <v>-0.4032</v>
       </c>
       <c r="I15">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="J15">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K15">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="L15">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="M15">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="N15">
         <v>4</v>
@@ -1099,34 +1099,34 @@
         <v>0</v>
       </c>
       <c r="D16">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="E16">
-        <v>1.6007</v>
+        <v>0.7129</v>
       </c>
       <c r="F16">
-        <v>1.6305</v>
+        <v>1.0556</v>
       </c>
       <c r="G16">
-        <v>0.0298</v>
+        <v>0.3427</v>
       </c>
       <c r="H16">
-        <v>-0.2705</v>
+        <v>2.3266</v>
       </c>
       <c r="I16">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J16">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="K16">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="L16">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M16">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="N16">
         <v>4</v>
@@ -1140,34 +1140,34 @@
         <v>15</v>
       </c>
       <c r="C17">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D17">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E17">
         <v>1.0358</v>
       </c>
       <c r="F17">
-        <v>1.0444</v>
+        <v>1.1311</v>
       </c>
       <c r="G17">
-        <v>0.0086</v>
+        <v>0.0953</v>
       </c>
       <c r="H17">
-        <v>0.0405</v>
+        <v>0.5301</v>
       </c>
       <c r="I17">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="J17">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="K17">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="L17">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="M17">
         <v>36</v>
@@ -1184,37 +1184,37 @@
         <v>16</v>
       </c>
       <c r="C18">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D18">
         <v>0</v>
       </c>
       <c r="E18">
-        <v>0.8925</v>
+        <v>1.0381</v>
       </c>
       <c r="F18">
-        <v>0.9111</v>
+        <v>0.9204</v>
       </c>
       <c r="G18">
-        <v>0.0186</v>
+        <v>-0.1176</v>
       </c>
       <c r="H18">
-        <v>0.1271</v>
+        <v>-0.1544</v>
       </c>
       <c r="I18">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="J18">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="K18">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="L18">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="M18">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="N18">
         <v>5</v>
@@ -1231,34 +1231,34 @@
         <v>0</v>
       </c>
       <c r="D19">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E19">
-        <v>1.6294</v>
+        <v>1.0312</v>
       </c>
       <c r="F19">
-        <v>1.5966</v>
+        <v>1.5523</v>
       </c>
       <c r="G19">
-        <v>-0.0328</v>
+        <v>0.5211</v>
       </c>
       <c r="H19">
-        <v>-0.3183</v>
+        <v>1.8989</v>
       </c>
       <c r="I19">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J19">
+        <v>10</v>
+      </c>
+      <c r="K19">
+        <v>9</v>
+      </c>
+      <c r="L19">
         <v>3</v>
       </c>
-      <c r="K19">
-        <v>3</v>
-      </c>
-      <c r="L19">
-        <v>4</v>
-      </c>
       <c r="M19">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="N19">
         <v>5</v>
@@ -1272,34 +1272,34 @@
         <v>15</v>
       </c>
       <c r="C20">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D20">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E20">
         <v>1.035</v>
       </c>
       <c r="F20">
-        <v>1.082</v>
+        <v>1.1874</v>
       </c>
       <c r="G20">
-        <v>0.047</v>
+        <v>0.1524</v>
       </c>
       <c r="H20">
-        <v>0.1151</v>
+        <v>0.5764</v>
       </c>
       <c r="I20">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="J20">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="K20">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="L20">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="M20">
         <v>35</v>
@@ -1316,37 +1316,37 @@
         <v>16</v>
       </c>
       <c r="C21">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D21">
         <v>0</v>
       </c>
       <c r="E21">
-        <v>0.8407</v>
+        <v>1.1071</v>
       </c>
       <c r="F21">
-        <v>0.905</v>
+        <v>1.0544</v>
       </c>
       <c r="G21">
-        <v>0.06419999999999999</v>
+        <v>-0.0527</v>
       </c>
       <c r="H21">
-        <v>0.2185</v>
+        <v>-0.0429</v>
       </c>
       <c r="I21">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="J21">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="K21">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="L21">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="M21">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="N21">
         <v>6</v>
@@ -1363,34 +1363,34 @@
         <v>0</v>
       </c>
       <c r="D22">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E22">
-        <v>2.2004</v>
+        <v>0.9129</v>
       </c>
       <c r="F22">
-        <v>2.1442</v>
+        <v>1.4125</v>
       </c>
       <c r="G22">
-        <v>-0.0563</v>
+        <v>0.4997</v>
       </c>
       <c r="H22">
-        <v>-0.5056</v>
+        <v>1.6245</v>
       </c>
       <c r="I22">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J22">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="K22">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L22">
         <v>3</v>
       </c>
       <c r="M22">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="N22">
         <v>6</v>
